--- a/AAII_Financials/Quarterly/TGT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>TGT</t>
   </si>
@@ -656,167 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45962</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45871</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45780</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45689</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45598</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45507</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45416</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45325</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>26539000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>25443000</v>
+      </c>
+      <c r="F8" s="3">
         <v>30453000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>25270000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>25211000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>23846000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>30915000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>25668000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>25452000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>24531000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>31919000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>25398000</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>18597000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>18061000</v>
+      </c>
+      <c r="F9" s="3">
         <v>22343000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>18137000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>17903000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>17128000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>22802000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>18402000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>17826000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>17471000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>23495000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>18149000</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7942000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7382000</v>
+      </c>
+      <c r="F10" s="3">
         <v>8110000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>7133000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>7308000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>6718000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>8113000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>7266000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>7626000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>7060000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>8424000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>7249000</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -830,8 +854,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,8 +891,14 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -900,78 +932,96 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-961000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>89000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>196000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>34000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>-593000</v>
+      </c>
+      <c r="J14" s="3">
         <v>31000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>36000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>4000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>651000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>685000</v>
+      </c>
+      <c r="F15" s="3">
         <v>681000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>649000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>632000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>655000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>646000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>639000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>626000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>618000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>622000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>616000</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -982,78 +1032,92 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24935000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>24293000</v>
+      </c>
+      <c r="F17" s="3">
         <v>28958000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>24101000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>23841000</v>
       </c>
-      <c r="G17" s="3">
-        <v>22349000</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>22942000</v>
+      </c>
+      <c r="J17" s="3">
         <v>29389000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>24471000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>23761000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>23206000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>30023000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>23992000</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1150000</v>
+      </c>
+      <c r="F18" s="3">
         <v>1495000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1169000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1370000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1497000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>904000</v>
+      </c>
+      <c r="J18" s="3">
         <v>1526000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1197000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1691000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1325000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1896000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1406000</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1067,183 +1131,215 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2000</v>
       </c>
       <c r="G20" s="3">
         <v>-1000</v>
       </c>
       <c r="H20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
+      <c r="J20" s="3">
+        <v>-1000</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2247000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1835000</v>
+      </c>
+      <c r="F21" s="3">
         <v>2177000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1819000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2000000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2153000</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>1560000</v>
+      </c>
+      <c r="J21" s="3">
         <v>2173000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1836000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2317000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1943000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2519000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2022000</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>117000</v>
+      </c>
+      <c r="F22" s="3">
         <v>99000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>115000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>116000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>116000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>90000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>105000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>110000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>106000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>107000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2459000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1033000</v>
+      </c>
+      <c r="F23" s="3">
         <v>1308000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>859000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1218000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1382000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1406000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1091000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1545000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1219000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1786000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1235000</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>582000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>252000</v>
+      </c>
+      <c r="F24" s="3">
         <v>263000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>170000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>283000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>346000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>303000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>237000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>353000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>277000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>404000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>264000</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1277,78 +1373,96 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1877000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>781000</v>
+      </c>
+      <c r="F26" s="3">
         <v>1045000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>689000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>935000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1036000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1103000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>854000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1192000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>942000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1382000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>971000</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1877000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>781000</v>
+      </c>
+      <c r="F27" s="3">
         <v>1045000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>689000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>935000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1036000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1103000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>854000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1192000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>942000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1382000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>971000</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1382,8 +1496,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1417,8 +1537,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1452,8 +1578,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1487,78 +1619,96 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
         <v>1000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2000</v>
       </c>
       <c r="G32" s="3">
         <v>1000</v>
       </c>
       <c r="H32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
+      <c r="J32" s="3">
+        <v>1000</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1877000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>781000</v>
+      </c>
+      <c r="F33" s="3">
         <v>1045000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>689000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>935000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1036000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1103000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>854000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1192000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>942000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1382000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>971000</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1592,83 +1742,101 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1877000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>781000</v>
+      </c>
+      <c r="F35" s="3">
         <v>1045000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>689000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>935000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1036000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1103000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>854000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1192000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>942000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1382000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>971000</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45962</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45871</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45780</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45689</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45598</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45507</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45416</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45325</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1682,8 +1850,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1697,43 +1867,51 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5411000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3534000</v>
+      </c>
+      <c r="F41" s="3">
         <v>5488000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3822000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4341000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2887000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4762000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3433000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3497000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3604000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3805000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1910000</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1767,253 +1945,301 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
         <v>1807000</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>1541000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>1404000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>13249000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>12317000</v>
+      </c>
+      <c r="F44" s="3">
         <v>12304000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>14896000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>12881000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>13048000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>12740000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>15165000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>12604000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>11730000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>11886000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>14731000</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2268000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2214000</v>
+      </c>
+      <c r="F45" s="3">
         <v>183000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1984000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1812000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1824000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>185000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1956000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1817000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1744000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>202000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1958000</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20928000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>18065000</v>
+      </c>
+      <c r="F46" s="3">
         <v>20005000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>20702000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>19034000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>17759000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>19454000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>20554000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>17918000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>17078000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>17498000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>18599000</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3">
         <v>2000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
         <v>3000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38354000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>37827000</v>
+      </c>
+      <c r="F48" s="3">
         <v>37452000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>37449000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>37262000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>36921000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>36785000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>36444000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>36620000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>36600000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>36458000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>36254000</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>631000</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>631000</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>631000</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2047,8 +2273,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2082,43 +2314,55 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1953000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2118000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1402000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1838000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1554000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1505000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>899000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1533000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1454000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1439000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>769000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1376000</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2152,43 +2396,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>61235000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>58010000</v>
+      </c>
+      <c r="F54" s="3">
         <v>59490000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>59991000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>57851000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>56185000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>57769000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>58531000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>55995000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>55117000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>55356000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>56229000</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2202,8 +2458,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2217,218 +2475,256 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13306000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>12188000</v>
+      </c>
+      <c r="F57" s="3">
         <v>12622000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>13792000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>12019000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>11823000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>13053000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>14419000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>12595000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11561000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>12098000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>14291000</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1537000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1509000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2502000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1516000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1508000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1500000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1989000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1982000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1982000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2948000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1445000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1439000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>959000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1015000</v>
+      </c>
+      <c r="F59" s="3">
         <v>3389000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>924000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1005000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1031000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3115000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>944000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>992000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1067000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3085000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>910000</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21180000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>19384000</v>
+      </c>
+      <c r="F60" s="3">
         <v>21230000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>21242000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>19223000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>18991000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>20799000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>21792000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>19984000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>19859000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>19304000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>21502000</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17659000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>17763000</v>
+      </c>
+      <c r="F61" s="3">
         <v>17788000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>18955000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>18894000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>17963000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>17886000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>17869000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>17180000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>17033000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>18201000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>18104000</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2049000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2030000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1684000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2014000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1901000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1946000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1727000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1962000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1907000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1842000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1487000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1662000</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2462,8 +2758,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2497,8 +2799,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2532,43 +2840,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>43392000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>41615000</v>
+      </c>
+      <c r="F66" s="3">
         <v>43325000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>44490000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>42431000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>41238000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>43103000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>44042000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>41566000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>41277000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>41924000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>43715000</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2582,8 +2902,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2617,8 +2939,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2652,8 +2980,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2687,8 +3021,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2722,43 +3062,55 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10890000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>9552000</v>
+      </c>
+      <c r="F72" s="3">
         <v>9297000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>8777000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>8766000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>8360000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>8090000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>8009000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>8030000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>7519000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>7093000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>6225000</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2792,8 +3144,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2827,8 +3185,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2862,43 +3226,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17843000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16395000</v>
+      </c>
+      <c r="F76" s="3">
         <v>16165000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>15501000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15420000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>14947000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>14666000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14489000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14429000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>13840000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13432000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>12514000</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2932,83 +3308,101 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45962</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45871</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45780</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45689</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45598</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45507</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45416</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45325</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1877000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>781000</v>
+      </c>
+      <c r="F81" s="3">
         <v>1045000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>689000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>935000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1036000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1103000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>854000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1192000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>942000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1382000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>971000</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3022,43 +3416,51 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>771000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>787000</v>
+      </c>
+      <c r="F83" s="3">
         <v>766000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>754000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>743000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>718000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>729000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>722000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>683000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>667000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>696000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>675000</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3092,8 +3494,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3127,8 +3535,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3162,8 +3576,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3197,8 +3617,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3232,43 +3658,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3803000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>716000</v>
+      </c>
+      <c r="F89" s="3">
         <v>3077000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1127000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2083000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>275000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>3289000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>739000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2238000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1101000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3289000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1934000</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3282,43 +3720,51 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1369000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1035000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-885000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-978000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1074000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-790000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-923000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-655000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-639000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-674000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-854000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1127000</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3352,8 +3798,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3387,43 +3839,55 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1364000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1033000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-859000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-937000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1066000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-787000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-918000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-637000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-634000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-671000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-850000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1089000</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3437,43 +3901,51 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>518000</v>
+      </c>
+      <c r="E96" s="3">
         <v>516000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
+        <v>516000</v>
+      </c>
+      <c r="G96" s="3">
         <v>518000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>509000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>510000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>513000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>516000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>509000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>508000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>508000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3507,8 +3979,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3542,8 +4020,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3577,43 +4061,55 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-562000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1637000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-552000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-709000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>437000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1363000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-166000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1711000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-631000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-544000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-552000</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3647,39 +4143,51 @@
       <c r="M101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1877000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1954000</v>
+      </c>
+      <c r="F102" s="3">
         <v>1666000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-519000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1454000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1875000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1329000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-64000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-107000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-201000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1895000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>293000</v>
       </c>
     </row>
